--- a/hints.xlsx
+++ b/hints.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Xenia160100\Documents\GitHub\aozakana\hint_test\hint_test\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{5B7BFB66-6E1A-42AD-8EB1-74654B4805E7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4F9B27EA-4740-4215-8355-77C9B93ADBB1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="21820" windowHeight="13900" xr2:uid="{E69F9E97-3D7F-4EEF-852A-49F659DA4124}"/>
   </bookViews>
@@ -931,15 +931,12 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1">
       <alignment vertical="center"/>
@@ -1488,7 +1485,7 @@
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.55000000000000004">
-      <c r="A16" s="3" t="s">
+      <c r="A16" s="2" t="s">
         <v>26</v>
       </c>
       <c r="B16" t="s">
@@ -1505,7 +1502,7 @@
       </c>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.55000000000000004">
-      <c r="A17" s="3" t="s">
+      <c r="A17" s="2" t="s">
         <v>26</v>
       </c>
       <c r="B17" t="s">
@@ -1536,7 +1533,7 @@
       </c>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.55000000000000004">
-      <c r="A19" s="3" t="s">
+      <c r="A19" s="2" t="s">
         <v>26</v>
       </c>
       <c r="B19" t="s">
@@ -1553,7 +1550,7 @@
       </c>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.55000000000000004">
-      <c r="A20" s="3" t="s">
+      <c r="A20" s="2" t="s">
         <v>26</v>
       </c>
       <c r="B20" t="s">
@@ -1584,7 +1581,7 @@
       </c>
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.55000000000000004">
-      <c r="A22" s="3" t="s">
+      <c r="A22" s="2" t="s">
         <v>26</v>
       </c>
       <c r="B22" t="s">
@@ -1601,7 +1598,7 @@
       </c>
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.55000000000000004">
-      <c r="A23" s="3" t="s">
+      <c r="A23" s="2" t="s">
         <v>26</v>
       </c>
       <c r="B23" t="s">
@@ -1632,7 +1629,7 @@
       </c>
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.55000000000000004">
-      <c r="A25" s="3" t="s">
+      <c r="A25" s="2" t="s">
         <v>26</v>
       </c>
       <c r="B25" t="s">
@@ -1649,7 +1646,7 @@
       </c>
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.55000000000000004">
-      <c r="A26" s="3" t="s">
+      <c r="A26" s="2" t="s">
         <v>26</v>
       </c>
       <c r="B26" t="s">
@@ -1675,12 +1672,12 @@
       <c r="C27" t="s">
         <v>11</v>
       </c>
-      <c r="E27" s="2" t="s">
+      <c r="E27" t="s">
         <v>67</v>
       </c>
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.55000000000000004">
-      <c r="A28" s="3" t="s">
+      <c r="A28" s="2" t="s">
         <v>26</v>
       </c>
       <c r="B28" t="s">
@@ -1697,7 +1694,7 @@
       </c>
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.55000000000000004">
-      <c r="A29" s="3" t="s">
+      <c r="A29" s="2" t="s">
         <v>26</v>
       </c>
       <c r="B29" t="s">
@@ -1723,7 +1720,7 @@
       <c r="C30" t="s">
         <v>11</v>
       </c>
-      <c r="E30" s="2" t="s">
+      <c r="E30" t="s">
         <v>68</v>
       </c>
     </row>
@@ -1737,7 +1734,7 @@
       <c r="C31" t="s">
         <v>56</v>
       </c>
-      <c r="E31" s="2" t="s">
+      <c r="E31" t="s">
         <v>69</v>
       </c>
     </row>
@@ -2073,21 +2070,21 @@
       <c r="C55" t="s">
         <v>8</v>
       </c>
-      <c r="E55" s="2" t="s">
+      <c r="E55" t="s">
         <v>101</v>
       </c>
     </row>
     <row r="56" spans="1:5" x14ac:dyDescent="0.55000000000000004">
-      <c r="A56" s="3" t="s">
+      <c r="A56" s="2" t="s">
         <v>90</v>
       </c>
       <c r="B56" t="s">
         <v>95</v>
       </c>
-      <c r="C56" s="3" t="s">
+      <c r="C56" s="2" t="s">
         <v>159</v>
       </c>
-      <c r="E56" s="2" t="s">
+      <c r="E56" t="s">
         <v>100</v>
       </c>
     </row>
@@ -2104,7 +2101,7 @@
       <c r="D57" t="s">
         <v>11</v>
       </c>
-      <c r="E57" s="2" t="s">
+      <c r="E57" t="s">
         <v>105</v>
       </c>
     </row>
@@ -2121,7 +2118,7 @@
       <c r="D58" t="s">
         <v>61</v>
       </c>
-      <c r="E58" s="2" t="s">
+      <c r="E58" t="s">
         <v>99</v>
       </c>
     </row>
@@ -2138,7 +2135,7 @@
       <c r="D59" t="s">
         <v>63</v>
       </c>
-      <c r="E59" s="2" t="s">
+      <c r="E59" t="s">
         <v>98</v>
       </c>
     </row>
@@ -2155,7 +2152,7 @@
       <c r="D60" t="s">
         <v>64</v>
       </c>
-      <c r="E60" s="2" t="s">
+      <c r="E60" t="s">
         <v>102</v>
       </c>
     </row>
@@ -2172,7 +2169,7 @@
       <c r="D61" t="s">
         <v>97</v>
       </c>
-      <c r="E61" s="2" t="s">
+      <c r="E61" t="s">
         <v>103</v>
       </c>
     </row>
@@ -2189,7 +2186,7 @@
       <c r="D62" t="s">
         <v>11</v>
       </c>
-      <c r="E62" s="2" t="s">
+      <c r="E62" t="s">
         <v>106</v>
       </c>
     </row>
@@ -2206,7 +2203,7 @@
       <c r="D63" t="s">
         <v>61</v>
       </c>
-      <c r="E63" s="2" t="s">
+      <c r="E63" t="s">
         <v>107</v>
       </c>
     </row>
@@ -2223,12 +2220,12 @@
       <c r="D64" t="s">
         <v>97</v>
       </c>
-      <c r="E64" s="2" t="s">
+      <c r="E64" t="s">
         <v>108</v>
       </c>
     </row>
     <row r="65" spans="1:5" x14ac:dyDescent="0.55000000000000004">
-      <c r="A65" s="3" t="s">
+      <c r="A65" s="2" t="s">
         <v>90</v>
       </c>
       <c r="B65" t="s">
@@ -2237,7 +2234,7 @@
       <c r="C65" t="s">
         <v>109</v>
       </c>
-      <c r="E65" s="2" t="s">
+      <c r="E65" t="s">
         <v>110</v>
       </c>
     </row>
@@ -2254,7 +2251,7 @@
       <c r="D66" t="s">
         <v>97</v>
       </c>
-      <c r="E66" s="2" t="s">
+      <c r="E66" t="s">
         <v>111</v>
       </c>
     </row>
@@ -2271,7 +2268,7 @@
       <c r="D67" t="s">
         <v>11</v>
       </c>
-      <c r="E67" s="2" t="s">
+      <c r="E67" t="s">
         <v>113</v>
       </c>
     </row>
@@ -2288,7 +2285,7 @@
       <c r="D68" t="s">
         <v>61</v>
       </c>
-      <c r="E68" s="2" t="s">
+      <c r="E68" t="s">
         <v>114</v>
       </c>
     </row>
@@ -2305,7 +2302,7 @@
       <c r="D69" t="s">
         <v>63</v>
       </c>
-      <c r="E69" s="2" t="s">
+      <c r="E69" t="s">
         <v>115</v>
       </c>
     </row>
@@ -2322,12 +2319,12 @@
       <c r="D70" t="s">
         <v>97</v>
       </c>
-      <c r="E70" s="2" t="s">
+      <c r="E70" t="s">
         <v>116</v>
       </c>
     </row>
     <row r="71" spans="1:5" x14ac:dyDescent="0.55000000000000004">
-      <c r="A71" s="3" t="s">
+      <c r="A71" s="2" t="s">
         <v>90</v>
       </c>
       <c r="B71" t="s">
@@ -2336,7 +2333,7 @@
       <c r="C71" t="s">
         <v>117</v>
       </c>
-      <c r="E71" s="2" t="s">
+      <c r="E71" t="s">
         <v>118</v>
       </c>
     </row>
@@ -2353,12 +2350,12 @@
       <c r="D72" t="s">
         <v>97</v>
       </c>
-      <c r="E72" s="2" t="s">
+      <c r="E72" t="s">
         <v>119</v>
       </c>
     </row>
     <row r="73" spans="1:5" x14ac:dyDescent="0.55000000000000004">
-      <c r="A73" s="3" t="s">
+      <c r="A73" s="2" t="s">
         <v>90</v>
       </c>
       <c r="B73" t="s">
@@ -2367,7 +2364,7 @@
       <c r="C73" t="s">
         <v>120</v>
       </c>
-      <c r="E73" s="2" t="s">
+      <c r="E73" t="s">
         <v>121</v>
       </c>
     </row>
@@ -2384,7 +2381,7 @@
       <c r="D74" t="s">
         <v>11</v>
       </c>
-      <c r="E74" s="2" t="s">
+      <c r="E74" t="s">
         <v>122</v>
       </c>
     </row>
@@ -2401,7 +2398,7 @@
       <c r="D75" t="s">
         <v>61</v>
       </c>
-      <c r="E75" s="2" t="s">
+      <c r="E75" t="s">
         <v>123</v>
       </c>
     </row>
@@ -2418,7 +2415,7 @@
       <c r="D76" t="s">
         <v>63</v>
       </c>
-      <c r="E76" s="2" t="s">
+      <c r="E76" t="s">
         <v>124</v>
       </c>
     </row>
@@ -2435,12 +2432,12 @@
       <c r="D77" t="s">
         <v>97</v>
       </c>
-      <c r="E77" s="2" t="s">
+      <c r="E77" t="s">
         <v>125</v>
       </c>
     </row>
     <row r="78" spans="1:5" x14ac:dyDescent="0.55000000000000004">
-      <c r="A78" s="3" t="s">
+      <c r="A78" s="2" t="s">
         <v>90</v>
       </c>
       <c r="B78" t="s">
@@ -2449,7 +2446,7 @@
       <c r="C78" t="s">
         <v>126</v>
       </c>
-      <c r="E78" s="2" t="s">
+      <c r="E78" t="s">
         <v>127</v>
       </c>
     </row>
@@ -2466,7 +2463,7 @@
       <c r="D79" t="s">
         <v>11</v>
       </c>
-      <c r="E79" s="2" t="s">
+      <c r="E79" t="s">
         <v>128</v>
       </c>
     </row>
@@ -2483,7 +2480,7 @@
       <c r="D80" t="s">
         <v>61</v>
       </c>
-      <c r="E80" s="2" t="s">
+      <c r="E80" t="s">
         <v>129</v>
       </c>
     </row>
@@ -2500,7 +2497,7 @@
       <c r="D81" t="s">
         <v>63</v>
       </c>
-      <c r="E81" s="2" t="s">
+      <c r="E81" t="s">
         <v>130</v>
       </c>
     </row>
@@ -2517,12 +2514,12 @@
       <c r="D82" t="s">
         <v>97</v>
       </c>
-      <c r="E82" s="2" t="s">
+      <c r="E82" t="s">
         <v>131</v>
       </c>
     </row>
     <row r="83" spans="1:5" x14ac:dyDescent="0.55000000000000004">
-      <c r="A83" s="3" t="s">
+      <c r="A83" s="2" t="s">
         <v>90</v>
       </c>
       <c r="B83" t="s">
@@ -2531,7 +2528,7 @@
       <c r="C83" t="s">
         <v>132</v>
       </c>
-      <c r="E83" s="2" t="s">
+      <c r="E83" t="s">
         <v>133</v>
       </c>
     </row>
@@ -2548,12 +2545,12 @@
       <c r="D84" t="s">
         <v>97</v>
       </c>
-      <c r="E84" s="2" t="s">
+      <c r="E84" t="s">
         <v>134</v>
       </c>
     </row>
     <row r="85" spans="1:5" x14ac:dyDescent="0.55000000000000004">
-      <c r="A85" s="3" t="s">
+      <c r="A85" s="2" t="s">
         <v>90</v>
       </c>
       <c r="B85" t="s">
@@ -2562,7 +2559,7 @@
       <c r="C85" t="s">
         <v>135</v>
       </c>
-      <c r="E85" s="2" t="s">
+      <c r="E85" t="s">
         <v>136</v>
       </c>
     </row>
@@ -2579,7 +2576,7 @@
       <c r="D86" t="s">
         <v>11</v>
       </c>
-      <c r="E86" s="2" t="s">
+      <c r="E86" t="s">
         <v>137</v>
       </c>
     </row>
@@ -2596,7 +2593,7 @@
       <c r="D87" t="s">
         <v>61</v>
       </c>
-      <c r="E87" s="2" t="s">
+      <c r="E87" t="s">
         <v>138</v>
       </c>
     </row>
@@ -2613,7 +2610,7 @@
       <c r="D88" t="s">
         <v>97</v>
       </c>
-      <c r="E88" s="2" t="s">
+      <c r="E88" t="s">
         <v>139</v>
       </c>
     </row>
@@ -2624,24 +2621,24 @@
       <c r="B89" t="s">
         <v>95</v>
       </c>
-      <c r="C89" s="4" t="s">
+      <c r="C89" s="3" t="s">
         <v>140</v>
       </c>
-      <c r="E89" s="2" t="s">
+      <c r="E89" t="s">
         <v>141</v>
       </c>
     </row>
     <row r="90" spans="1:5" x14ac:dyDescent="0.55000000000000004">
-      <c r="A90" s="3" t="s">
+      <c r="A90" s="2" t="s">
         <v>90</v>
       </c>
       <c r="B90" t="s">
         <v>142</v>
       </c>
-      <c r="C90" s="5" t="s">
+      <c r="C90" s="4" t="s">
         <v>159</v>
       </c>
-      <c r="E90" s="2" t="s">
+      <c r="E90" t="s">
         <v>143</v>
       </c>
     </row>
@@ -2658,7 +2655,7 @@
       <c r="D91" t="s">
         <v>11</v>
       </c>
-      <c r="E91" s="2" t="s">
+      <c r="E91" t="s">
         <v>145</v>
       </c>
     </row>
@@ -2675,12 +2672,12 @@
       <c r="D92" t="s">
         <v>97</v>
       </c>
-      <c r="E92" s="2" t="s">
+      <c r="E92" t="s">
         <v>146</v>
       </c>
     </row>
     <row r="93" spans="1:5" x14ac:dyDescent="0.55000000000000004">
-      <c r="A93" s="3" t="s">
+      <c r="A93" s="2" t="s">
         <v>90</v>
       </c>
       <c r="B93" t="s">
@@ -2689,7 +2686,7 @@
       <c r="C93" t="s">
         <v>147</v>
       </c>
-      <c r="E93" s="2" t="s">
+      <c r="E93" t="s">
         <v>148</v>
       </c>
     </row>
@@ -2706,7 +2703,7 @@
       <c r="D94" t="s">
         <v>11</v>
       </c>
-      <c r="E94" s="2" t="s">
+      <c r="E94" t="s">
         <v>149</v>
       </c>
     </row>
@@ -2723,7 +2720,7 @@
       <c r="D95" t="s">
         <v>61</v>
       </c>
-      <c r="E95" s="2" t="s">
+      <c r="E95" t="s">
         <v>150</v>
       </c>
     </row>
@@ -2740,21 +2737,21 @@
       <c r="D96" t="s">
         <v>97</v>
       </c>
-      <c r="E96" s="2" t="s">
+      <c r="E96" t="s">
         <v>151</v>
       </c>
     </row>
     <row r="97" spans="1:5" x14ac:dyDescent="0.55000000000000004">
-      <c r="A97" s="3" t="s">
+      <c r="A97" s="2" t="s">
         <v>90</v>
       </c>
       <c r="B97" t="s">
         <v>142</v>
       </c>
-      <c r="C97" s="4" t="s">
+      <c r="C97" s="3" t="s">
         <v>152</v>
       </c>
-      <c r="E97" s="2" t="s">
+      <c r="E97" t="s">
         <v>153</v>
       </c>
     </row>
@@ -2765,27 +2762,27 @@
       <c r="B98" t="s">
         <v>142</v>
       </c>
-      <c r="C98" s="4" t="s">
+      <c r="C98" s="3" t="s">
         <v>152</v>
       </c>
       <c r="D98" t="s">
         <v>97</v>
       </c>
-      <c r="E98" s="2" t="s">
+      <c r="E98" t="s">
         <v>154</v>
       </c>
     </row>
     <row r="99" spans="1:5" x14ac:dyDescent="0.55000000000000004">
-      <c r="A99" s="3" t="s">
+      <c r="A99" s="2" t="s">
         <v>90</v>
       </c>
       <c r="B99" t="s">
         <v>142</v>
       </c>
-      <c r="C99" s="4" t="s">
+      <c r="C99" s="3" t="s">
         <v>155</v>
       </c>
-      <c r="E99" s="2" t="s">
+      <c r="E99" t="s">
         <v>156</v>
       </c>
     </row>
@@ -2796,13 +2793,13 @@
       <c r="B100" t="s">
         <v>142</v>
       </c>
-      <c r="C100" s="4" t="s">
+      <c r="C100" s="3" t="s">
         <v>155</v>
       </c>
       <c r="D100" t="s">
         <v>11</v>
       </c>
-      <c r="E100" s="2" t="s">
+      <c r="E100" t="s">
         <v>157</v>
       </c>
     </row>
@@ -2813,30 +2810,30 @@
       <c r="B101" t="s">
         <v>142</v>
       </c>
-      <c r="C101" s="4" t="s">
+      <c r="C101" s="3" t="s">
         <v>155</v>
       </c>
       <c r="D101" t="s">
         <v>97</v>
       </c>
-      <c r="E101" s="2" t="s">
+      <c r="E101" t="s">
         <v>158</v>
       </c>
     </row>
     <row r="102" spans="1:5" x14ac:dyDescent="0.55000000000000004">
-      <c r="C102" s="4"/>
+      <c r="C102" s="3"/>
     </row>
     <row r="103" spans="1:5" x14ac:dyDescent="0.55000000000000004">
-      <c r="C103" s="4"/>
+      <c r="C103" s="3"/>
     </row>
     <row r="104" spans="1:5" x14ac:dyDescent="0.55000000000000004">
-      <c r="C104" s="4"/>
+      <c r="C104" s="3"/>
     </row>
     <row r="105" spans="1:5" x14ac:dyDescent="0.55000000000000004">
-      <c r="C105" s="4"/>
+      <c r="C105" s="3"/>
     </row>
     <row r="106" spans="1:5" x14ac:dyDescent="0.55000000000000004">
-      <c r="C106" s="4"/>
+      <c r="C106" s="3"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1"/>

--- a/hints.xlsx
+++ b/hints.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Xenia160100\Documents\GitHub\aozakana\hint_test\hint_test\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4F9B27EA-4740-4215-8355-77C9B93ADBB1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:9_{6A0C1CC8-FABB-4399-8FA0-3BBF52C4F186}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="21820" windowHeight="13900" xr2:uid="{E69F9E97-3D7F-4EEF-852A-49F659DA4124}"/>
   </bookViews>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="448" uniqueCount="160">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="446" uniqueCount="159">
   <si>
     <t>Level1</t>
   </si>
@@ -867,10 +867,6 @@
   </si>
   <si>
     <t>&lt;b&gt;あまのがわ（天の川）&lt;/b&gt;&lt;br&gt;立方体を「し」のマスに配置して転がしていくと、「こた？？あまのか（が）わ」と読むことができます。&lt;br&gt;前半が「答えは～」と書いてあると推測すれば、単語になる「あまのがわ」が答えだと推測できます。</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>XXXX</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -951,8 +947,21 @@
   <cellStyles count="1">
     <cellStyle name="標準" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
+  <dxfs count="1">
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFCCCC"/>
+        </patternFill>
+      </fill>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <mruColors>
+      <color rgb="FFFFCCCC"/>
+    </mruColors>
+  </colors>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
@@ -2081,9 +2090,7 @@
       <c r="B56" t="s">
         <v>95</v>
       </c>
-      <c r="C56" s="2" t="s">
-        <v>159</v>
-      </c>
+      <c r="C56" s="2"/>
       <c r="E56" t="s">
         <v>100</v>
       </c>
@@ -2635,9 +2642,7 @@
       <c r="B90" t="s">
         <v>142</v>
       </c>
-      <c r="C90" s="4" t="s">
-        <v>159</v>
-      </c>
+      <c r="C90" s="4"/>
       <c r="E90" t="s">
         <v>143</v>
       </c>
@@ -2837,6 +2842,11 @@
     </row>
   </sheetData>
   <phoneticPr fontId="1"/>
+  <conditionalFormatting sqref="A1:XFD1048576">
+    <cfRule type="containsBlanks" dxfId="0" priority="1">
+      <formula>LEN(TRIM(A1))=0</formula>
+    </cfRule>
+  </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>